--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -536,14 +536,14 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>01w24</t>
+          <t>00_350</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>48149</v>
+        <v>44309</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -551,42 +551,42 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2447547.16</v>
+        <v>2251792.29</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2447547.16</v>
+        <v>2251796.97</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2492096.56</v>
+        <v>2321788.93</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.82</v>
+        <v>3.11</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00_350.csv</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>10wLim</t>
+          <t>01w24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43864</v>
+        <v>48149</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -594,42 +594,42 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2228923.93</v>
+        <v>2447547.16</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2228923.93</v>
+        <v>2447547.16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2261986.84</v>
+        <v>2492096.56</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>5072h</t>
+          <t>10wLim</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46028</v>
+        <v>43864</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -637,42 +637,42 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2338453.5</v>
+        <v>2228923.93</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2338459.2</v>
+        <v>2228923.93</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2379435.43</v>
+        <v>2261986.84</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>50wLim</t>
+          <t>5072h</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>47400</v>
+        <v>46028</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -680,42 +680,42 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2409050.89</v>
+        <v>2338453.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2409057.53</v>
+        <v>2338459.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2450491.16</v>
+        <v>2379435.43</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>75w00</t>
+          <t>50wLim</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>49890</v>
+        <v>47400</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -723,42 +723,42 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2537623.54</v>
+        <v>2409050.89</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2537623.54</v>
+        <v>2409057.53</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2591364.94</v>
+        <v>2450491.16</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>heu_full</t>
+          <t>75w00</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>44127</v>
+        <v>49890</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>572</v>
+        <v>227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -766,42 +766,42 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2244053.44</v>
+        <v>2537623.54</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2244177.41</v>
+        <v>2537623.54</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2583535.61</v>
+        <v>2591364.94</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15.13</v>
+        <v>2.12</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>heu_lim</t>
+          <t>heu_full</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>43812</v>
+        <v>44127</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -809,26 +809,69 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2226392.05</v>
+        <v>2244053.44</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2226520.62</v>
+        <v>2244177.41</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2549352.76</v>
+        <v>2583535.61</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>14.51</v>
+        <v>15.13</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0.01</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>heu_lim</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>43812</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sucesso</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2226392.05</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2226520.62</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2549352.76</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
         </is>

--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resultados_Custos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Custos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,16 +45,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -431,75 +441,87 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="92" customWidth="1" min="10" max="10"/>
     <col width="97" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nome da Instância</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total de Entregas</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pico de Abastecimento (Max/Dia)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Custo Modelo Exato (M1)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Custo Modelo Anual (M2)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Custo Heurística</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gap Heurística vs M1 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gap M2 vs M1 (%)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Caminho da Entrada</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pasta de Saída</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Qtd Dias</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Custo Projetado (365d)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>43750</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>501</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,20 +529,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>2223257.66</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>2223489.44</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>2467920.5</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0.01</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2223257.66</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2223489.44</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2467920.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -532,17 +564,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>00_350</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>44309</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>315</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -550,20 +584,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>2251792.29</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2251796.97</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>2321788.93</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2251792.29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2251796.97</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2321788.93</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,17 +619,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>01w24</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>48149</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>230</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -593,20 +639,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>2447547.16</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2447547.16</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2492096.56</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2447547.16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2447547.16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2492096.56</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -618,17 +674,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>10wLim</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>43864</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>259</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -636,20 +694,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>2228923.93</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2228923.93</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2261986.84</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2228923.93</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2228923.93</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2261986.84</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -661,17 +729,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5072h</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>46028</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>202</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -679,20 +749,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>2338453.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2338459.2</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>2379435.43</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2338453.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2338459.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2379435.43</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -704,17 +784,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>50wLim</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>47400</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>212</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -722,20 +804,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>2409050.89</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>2409057.53</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>2450491.16</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2409050.89</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2409057.53</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2450491.16</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -747,17 +839,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>75w00</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>49890</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>227</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -765,20 +859,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>2537623.54</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>2537623.54</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>2591364.94</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2537623.54</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2537623.54</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2591364.94</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -790,17 +894,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>heu_full</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>44127</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>572</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -808,20 +914,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>2244053.44</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>2244177.41</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>2583535.61</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.01</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2244053.44</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2244177.41</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2583535.61</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>15.13</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -833,17 +949,19 @@
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>heu_lim</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>43812</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>578</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -851,20 +969,30 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>2226392.05</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>2226520.62</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2549352.76</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0.01</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2226392.05</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2226520.62</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2549352.76</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>14.51</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -874,6 +1002,82 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>resultados_sliding_45_14</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>59021</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>629</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sucesso (Sliding)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3021346.57</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>355</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3106454.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>resultados_sliding_90_14</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>42158</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>532</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sucesso (Sliding)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2148117.95</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>318</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2465607.08</t>
         </is>
       </c>
     </row>

--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -55,13 +55,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -529,30 +531,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2223257.66</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2223489.44</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2467920.5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+      <c r="E2" s="4" t="n">
+        <v>2223257.66</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2223489.44</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>2467920.5</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -584,30 +576,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2251792.29</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2251796.97</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2321788.93</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E3" s="4" t="n">
+        <v>2251792.29</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2251796.97</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>2321788.93</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -639,30 +621,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2447547.16</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2447547.16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2492096.56</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E4" s="4" t="n">
+        <v>2447547.16</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2447547.16</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2492096.56</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -694,30 +666,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2228923.93</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2228923.93</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2261986.84</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E5" s="4" t="n">
+        <v>2228923.93</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2228923.93</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>2261986.84</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -749,30 +711,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2338453.5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2338459.2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2379435.43</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E6" s="4" t="n">
+        <v>2338453.5</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2338459.2</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2379435.43</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -804,30 +756,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2409050.89</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2409057.53</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2450491.16</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E7" s="4" t="n">
+        <v>2409050.89</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2409057.53</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2450491.16</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -859,30 +801,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2537623.54</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2537623.54</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2591364.94</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="E8" s="4" t="n">
+        <v>2537623.54</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2537623.54</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2591364.94</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -914,30 +846,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2244053.44</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2244177.41</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2583535.61</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+      <c r="E9" s="4" t="n">
+        <v>2244053.44</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2244177.41</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2583535.61</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -969,30 +891,20 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2226392.05</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2226520.62</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2549352.76</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>14.51</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+      <c r="E10" s="4" t="n">
+        <v>2226392.05</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2226520.62</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2549352.76</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1024,10 +936,8 @@
           <t>Sucesso (Sliding)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3021346.57</t>
-        </is>
+      <c r="E11" s="4" t="n">
+        <v>3021346.57</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1038,10 +948,8 @@
       <c r="L11" t="n">
         <v>355</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3106454.93</t>
-        </is>
+      <c r="M11" s="4" t="n">
+        <v>3106454.93</v>
       </c>
     </row>
     <row r="12">
@@ -1061,10 +969,8 @@
           <t>Sucesso (Sliding)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2148117.95</t>
-        </is>
+      <c r="E12" s="4" t="n">
+        <v>2148117.95</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1075,10 +981,107 @@
       <c r="L12" t="n">
         <v>318</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2465607.08</t>
-        </is>
+      <c r="M12" s="4" t="n">
+        <v>2465607.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>sliding_60_14_3</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>53510</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sucesso (Sliding)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>2722370.33</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>365</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>2722370.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>sliding_90_14_3</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>49560</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sucesso (Sliding)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2526656.37</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>365</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>2526656.37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>sliding_120_14_3</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>48518</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>581</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sucesso (Sliding)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2466054.23</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>365</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>2466054.23</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -480,35 +480,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Custo Alocação Original</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Custo Heurística</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gap Heurística vs M1 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gap M2 vs M1 (%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Caminho da Entrada</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pasta de Saída</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qtd Dias</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Custo Projetado (365d)</t>
         </is>
@@ -538,26 +543,27 @@
         <v>2223489.44</v>
       </c>
       <c r="G2" s="4" t="n">
+        <v>2845265.79</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>2467920.5</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00.csv</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -583,26 +589,27 @@
         <v>2251796.97</v>
       </c>
       <c r="G3" s="4" t="n">
+        <v>2880644.2</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>2321788.93</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>3.11</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00_350.csv</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -628,26 +635,27 @@
         <v>2447547.16</v>
       </c>
       <c r="G4" s="4" t="n">
+        <v>3128675.16</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>2492096.56</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -673,26 +681,27 @@
         <v>2228923.93</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>2853328.28</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>2261986.84</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>1.48</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -718,26 +727,27 @@
         <v>2338459.2</v>
       </c>
       <c r="G6" s="4" t="n">
+        <v>2992393.1</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>2379435.43</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>1.75</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -763,26 +773,27 @@
         <v>2409057.53</v>
       </c>
       <c r="G7" s="4" t="n">
+        <v>3082488.75</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>2450491.16</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>1.72</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -808,26 +819,27 @@
         <v>2537623.54</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>3241183.97</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>2591364.94</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>2.12</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -853,26 +865,27 @@
         <v>2244177.41</v>
       </c>
       <c r="G9" s="4" t="n">
+        <v>2879155.22</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>2583535.61</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>15.13</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -898,26 +911,27 @@
         <v>2226520.62</v>
       </c>
       <c r="G10" s="4" t="n">
+        <v>2849433.23</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>2549352.76</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>14.51</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -939,16 +953,10 @@
       <c r="E11" s="4" t="n">
         <v>3021346.57</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>355</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>3106454.93</v>
       </c>
     </row>
@@ -972,16 +980,10 @@
       <c r="E12" s="4" t="n">
         <v>2148117.95</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>318</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>2465607.08</v>
       </c>
     </row>
@@ -1005,16 +1007,10 @@
       <c r="E13" s="4" t="n">
         <v>2722370.33</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>365</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>2722370.33</v>
       </c>
     </row>
@@ -1038,16 +1034,10 @@
       <c r="E14" s="4" t="n">
         <v>2526656.37</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>365</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>2526656.37</v>
       </c>
     </row>
@@ -1071,16 +1061,10 @@
       <c r="E15" s="4" t="n">
         <v>2466054.23</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>365</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>2466054.23</v>
       </c>
     </row>

--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -429,22 +429,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="92" customWidth="1" min="10" max="10"/>
-    <col width="97" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="33" customWidth="1" min="19" max="19"/>
+    <col width="92" customWidth="1" min="20" max="20"/>
+    <col width="97" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,50 +480,95 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Custo Modelo Exato (M1)</t>
+          <t>Custo M1 Diário</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Custo M1 Anual</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Custo Modelo Anual (M2)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Custo Alocação Original</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Custo Heurística</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Heurística vs M1 (%)</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Gap M2 vs M1 (%)</t>
+          <t>Gap M1 Anual vs M1 Diário (%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Gap M2 vs M1 Diário (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Gap M2 vs M1 Anual (%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Heurística vs M1 Diário (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Heurística vs M1 Anual (%)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Heurística vs M2 (%)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Original vs M1 Diário (%)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Original vs M1 Anual (%)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Original vs M2 (%)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Gap Original vs Heurística (%)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Caminho da Entrada</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Pasta de Saída</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Qtd Dias</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Custo Projetado (365d)</t>
         </is>
@@ -540,30 +595,59 @@
         <v>2223257.66</v>
       </c>
       <c r="F2" s="4" t="n">
+        <v>1651961.02</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>2223489.44</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>2845265.79</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>2467920.5</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="M2" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" s="5" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00.csv</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -586,30 +670,59 @@
         <v>2251792.29</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>1631784.92</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>2251796.97</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>2880644.2</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>2321788.93</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
+        <v>-27.53</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M3" s="5" t="n">
         <v>3.11</v>
       </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" s="5" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00_350.csv</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -632,30 +745,59 @@
         <v>2447547.16</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>1769937.39</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>2447547.16</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>3128675.16</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>2492096.56</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
+        <v>-27.69</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" s="5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -678,30 +820,59 @@
         <v>2228923.93</v>
       </c>
       <c r="F5" s="4" t="n">
+        <v>1608397.4</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>2228923.93</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>2853328.28</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>2261986.84</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
+        <v>-27.84</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="M5" s="5" t="n">
         <v>1.48</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" s="5" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -724,30 +895,59 @@
         <v>2338453.5</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>1691970.72</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>2338459.2</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>2992393.1</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>2379435.43</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
+        <v>-27.65</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="M6" s="5" t="n">
         <v>1.75</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" s="5" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -770,30 +970,59 @@
         <v>2409050.89</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>1742818.55</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>2409057.53</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>3082488.75</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>2450491.16</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
+        <v>-27.66</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="M7" s="5" t="n">
         <v>1.72</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" s="5" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -816,30 +1045,59 @@
         <v>2537623.54</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>1833876.28</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>2537623.54</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>3241183.97</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>2591364.94</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
+        <v>-27.73</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="M8" s="5" t="n">
         <v>2.12</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" s="5" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -862,30 +1120,59 @@
         <v>2244053.44</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>1678633.51</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>2244177.41</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>2879155.22</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>2583535.61</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="M9" s="5" t="n">
         <v>15.13</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" s="5" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -908,30 +1195,59 @@
         <v>2226392.05</v>
       </c>
       <c r="F10" s="4" t="n">
+        <v>1653185.87</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>2226520.62</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>2849433.23</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>2549352.76</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
+        <v>-25.75</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>14.51</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" s="5" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -953,10 +1269,26 @@
       <c r="E11" s="4" t="n">
         <v>3021346.57</v>
       </c>
-      <c r="M11" t="n">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
         <v>355</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>3106454.93</v>
       </c>
     </row>
@@ -980,10 +1312,26 @@
       <c r="E12" s="4" t="n">
         <v>2148117.95</v>
       </c>
-      <c r="M12" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>318</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="W12" s="4" t="n">
         <v>2465607.08</v>
       </c>
     </row>
@@ -1007,10 +1355,26 @@
       <c r="E13" s="4" t="n">
         <v>2722370.33</v>
       </c>
-      <c r="M13" t="n">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
         <v>365</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>2722370.33</v>
       </c>
     </row>
@@ -1034,10 +1398,26 @@
       <c r="E14" s="4" t="n">
         <v>2526656.37</v>
       </c>
-      <c r="M14" t="n">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>365</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>2526656.37</v>
       </c>
     </row>
@@ -1061,10 +1441,26 @@
       <c r="E15" s="4" t="n">
         <v>2466054.23</v>
       </c>
-      <c r="M15" t="n">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
         <v>365</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="W15" s="4" t="n">
         <v>2466054.23</v>
       </c>
     </row>

--- a/alocacao/saidas_2/resumo_custos.xlsx
+++ b/alocacao/saidas_2/resumo_custos.xlsx
@@ -1,154 +1,335 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Custos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resultados_Custos" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+  <si>
+    <t xml:space="preserve">Nome da Instância</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de Entregas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pico de Abastecimento (Max/Dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo M1 Diário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo M1 Anual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo Modelo Anual (M2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo Alocação Original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo Heurística</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap M1 Anual vs M1 Diário (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap M2 vs M1 Diário (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap M2 vs M1 Anual (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Heurística vs M1 Diário (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Heurística vs M1 Anual (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Heurística vs M2 (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Original vs M1 Diário (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Original vs M1 Anual (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Original vs M2 (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Original vs Heurística (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caminho da Entrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta de Saída</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qtd Dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo Projetado (365d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sucesso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00_350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00_350.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01w24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10wLim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5072h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50wLim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75w00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heu_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heu_lim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resultados_sliding_45_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sucesso (Sliding)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resultados_sliding_90_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sliding_60_14_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sliding_90_14_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sliding_120_14_3</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+  </numFmts>
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -183,402 +364,244 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
-    <col width="31" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="33" customWidth="1" min="19" max="19"/>
-    <col width="92" customWidth="1" min="20" max="20"/>
-    <col width="97" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="25"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nome da Instância</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total de Entregas</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Pico de Abastecimento (Max/Dia)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Custo M1 Diário</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Custo M1 Anual</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Custo Modelo Anual (M2)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Custo Alocação Original</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Custo Heurística</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Gap M1 Anual vs M1 Diário (%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Gap M2 vs M1 Diário (%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gap M2 vs M1 Anual (%)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Heurística vs M1 Diário (%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Heurística vs M1 Anual (%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Heurística vs M2 (%)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Original vs M1 Diário (%)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Original vs M1 Anual (%)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Original vs M2 (%)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Gap Original vs Heurística (%)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Caminho da Entrada</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Pasta de Saída</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Qtd Dias</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Custo Projetado (365d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>43750</v>
@@ -586,10 +609,8 @@
       <c r="C2" s="3" t="n">
         <v>501</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D2" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>2223257.66</v>
@@ -628,7 +649,7 @@
         <v>27.98</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>72.23999999999999</v>
+        <v>72.24</v>
       </c>
       <c r="R2" s="5" t="n">
         <v>27.96</v>
@@ -636,35 +657,25 @@
       <c r="S2" s="5" t="n">
         <v>15.29</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00.csv</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>00_350</t>
-        </is>
+      <c r="T2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>44309</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+        <v>350</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>2251792.29</v>
@@ -711,24 +722,16 @@
       <c r="S3" s="5" t="n">
         <v>24.07</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00_350.csv</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_00_350</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>01w24</t>
-        </is>
+      <c r="T3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>48149</v>
@@ -736,10 +739,8 @@
       <c r="C4" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D4" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>2447547.16</v>
@@ -786,24 +787,16 @@
       <c r="S4" s="5" t="n">
         <v>25.54</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\01w24.csv</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_01w24</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>10wLim</t>
-        </is>
+      <c r="T4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>43864</v>
@@ -811,10 +804,8 @@
       <c r="C5" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D5" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2228923.93</v>
@@ -853,7 +844,7 @@
         <v>28.01</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.4</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>28.01</v>
@@ -861,24 +852,16 @@
       <c r="S5" s="5" t="n">
         <v>26.14</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\10wLim.csv</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_10wLim</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5072h</t>
-        </is>
+      <c r="T5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>46028</v>
@@ -886,10 +869,8 @@
       <c r="C6" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D6" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2338453.5</v>
@@ -936,24 +917,16 @@
       <c r="S6" s="5" t="n">
         <v>25.76</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\5072h.csv</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_5072h</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>50wLim</t>
-        </is>
+      <c r="T6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="U6" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>47400</v>
@@ -961,10 +934,8 @@
       <c r="C7" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D7" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>2409050.89</v>
@@ -1011,24 +982,16 @@
       <c r="S7" s="5" t="n">
         <v>25.79</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\50wLim.csv</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_50wLim</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>75w00</t>
-        </is>
+      <c r="T7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>49890</v>
@@ -1036,10 +999,8 @@
       <c r="C8" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D8" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>2537623.54</v>
@@ -1078,7 +1039,7 @@
         <v>27.73</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>76.73999999999999</v>
+        <v>76.74</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>27.73</v>
@@ -1086,24 +1047,16 @@
       <c r="S8" s="5" t="n">
         <v>25.08</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\75w00.csv</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_75w00</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>heu_full</t>
-        </is>
+      <c r="T8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>44127</v>
@@ -1111,10 +1064,8 @@
       <c r="C9" s="3" t="n">
         <v>572</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D9" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>2244053.44</v>
@@ -1161,24 +1112,16 @@
       <c r="S9" s="5" t="n">
         <v>11.44</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_full</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>heu_lim</t>
-        </is>
+      <c r="T9" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>43812</v>
@@ -1186,10 +1129,8 @@
       <c r="C10" s="3" t="n">
         <v>578</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
+      <c r="D10" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>2226392.05</v>
@@ -1236,24 +1177,16 @@
       <c r="S10" s="5" t="n">
         <v>11.77</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_2\alocacao_heu_lim</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>resultados_sliding_45_14</t>
-        </is>
+      <c r="T10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="U10" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>59021</v>
@@ -1261,42 +1194,22 @@
       <c r="C11" s="3" t="n">
         <v>629</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sucesso (Sliding)</t>
-        </is>
+      <c r="D11" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>3021346.57</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="V11" s="0" t="n">
         <v>355</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>3106454.93</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>resultados_sliding_90_14</t>
-        </is>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>42158</v>
@@ -1304,42 +1217,22 @@
       <c r="C12" s="3" t="n">
         <v>532</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sucesso (Sliding)</t>
-        </is>
+      <c r="D12" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>2148117.95</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="V12" s="0" t="n">
         <v>318</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>2465607.08</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>sliding_60_14_3</t>
-        </is>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>53510</v>
@@ -1347,42 +1240,22 @@
       <c r="C13" s="3" t="n">
         <v>538</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sucesso (Sliding)</t>
-        </is>
+      <c r="D13" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2722370.33</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="V13" s="0" t="n">
         <v>365</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>2722370.33</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>sliding_90_14_3</t>
-        </is>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>49560</v>
@@ -1390,42 +1263,22 @@
       <c r="C14" s="3" t="n">
         <v>592</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sucesso (Sliding)</t>
-        </is>
+      <c r="D14" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>2526656.37</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
+      <c r="V14" s="0" t="n">
         <v>365</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>2526656.37</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>sliding_120_14_3</t>
-        </is>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>48518</v>
@@ -1433,31 +1286,13 @@
       <c r="C15" s="3" t="n">
         <v>581</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sucesso (Sliding)</t>
-        </is>
+      <c r="D15" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>2466054.23</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
+      <c r="V15" s="0" t="n">
         <v>365</v>
       </c>
       <c r="W15" s="4" t="n">
@@ -1465,6 +1300,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>